--- a/Codes/Trial 1/Trial1_LSTM_Leaders_Results.xlsx
+++ b/Codes/Trial 1/Trial1_LSTM_Leaders_Results.xlsx
@@ -470,13 +470,13 @@
         <v>2020</v>
       </c>
       <c r="C2" t="n">
-        <v>7.410000000000005</v>
+        <v>16.7</v>
       </c>
       <c r="D2" t="n">
-        <v>1.559368491172791</v>
+        <v>2.119367122650146</v>
       </c>
       <c r="E2" t="n">
-        <v>5.850631508827214</v>
+        <v>14.58063287734985</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -494,13 +494,13 @@
         <v>2021</v>
       </c>
       <c r="C3" t="n">
-        <v>14.92</v>
+        <v>20.91</v>
       </c>
       <c r="D3" t="n">
-        <v>4.2504563331604</v>
+        <v>2.463904619216919</v>
       </c>
       <c r="E3" t="n">
-        <v>10.6695436668396</v>
+        <v>18.44609538078308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -518,13 +518,13 @@
         <v>2022</v>
       </c>
       <c r="C4" t="n">
-        <v>16.7</v>
+        <v>18.57999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>8.774555206298828</v>
+        <v>1.362436532974243</v>
       </c>
       <c r="E4" t="n">
-        <v>7.925444793701168</v>
+        <v>17.21756346702575</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -542,13 +542,13 @@
         <v>2023</v>
       </c>
       <c r="C5" t="n">
-        <v>20.91</v>
+        <v>4.48</v>
       </c>
       <c r="D5" t="n">
-        <v>11.86526966094971</v>
+        <v>0.7663015723228455</v>
       </c>
       <c r="E5" t="n">
-        <v>9.044730339050297</v>
+        <v>3.713698427677155</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -566,13 +566,13 @@
         <v>2024</v>
       </c>
       <c r="C6" t="n">
-        <v>18.57999999999999</v>
+        <v>6.740000000000003</v>
       </c>
       <c r="D6" t="n">
-        <v>13.62242984771729</v>
+        <v>1.478734612464905</v>
       </c>
       <c r="E6" t="n">
-        <v>4.95757015228271</v>
+        <v>5.261265387535098</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -590,13 +590,13 @@
         <v>2020</v>
       </c>
       <c r="C7" t="n">
-        <v>4.48</v>
+        <v>11.32</v>
       </c>
       <c r="D7" t="n">
-        <v>1.710031270980835</v>
+        <v>2.047784090042114</v>
       </c>
       <c r="E7" t="n">
-        <v>2.769968729019165</v>
+        <v>9.272215909957884</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -614,13 +614,13 @@
         <v>2021</v>
       </c>
       <c r="C8" t="n">
-        <v>6.740000000000003</v>
+        <v>20.59</v>
       </c>
       <c r="D8" t="n">
-        <v>4.052731037139893</v>
+        <v>2.425626993179321</v>
       </c>
       <c r="E8" t="n">
-        <v>2.68726896286011</v>
+        <v>18.16437300682068</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -638,13 +638,13 @@
         <v>2022</v>
       </c>
       <c r="C9" t="n">
-        <v>11.32</v>
+        <v>29.38</v>
       </c>
       <c r="D9" t="n">
-        <v>8.223476409912109</v>
+        <v>1.060881733894348</v>
       </c>
       <c r="E9" t="n">
-        <v>3.096523590087889</v>
+        <v>28.31911826610565</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -662,13 +662,13 @@
         <v>2023</v>
       </c>
       <c r="C10" t="n">
-        <v>20.59</v>
+        <v>2.61</v>
       </c>
       <c r="D10" t="n">
-        <v>11.22776412963867</v>
+        <v>0.9105565547943115</v>
       </c>
       <c r="E10" t="n">
-        <v>9.362235870361332</v>
+        <v>1.699443445205688</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -686,13 +686,13 @@
         <v>2024</v>
       </c>
       <c r="C11" t="n">
-        <v>29.38</v>
+        <v>2.28</v>
       </c>
       <c r="D11" t="n">
-        <v>14.54551315307617</v>
+        <v>1.628518462181091</v>
       </c>
       <c r="E11" t="n">
-        <v>14.83448684692382</v>
+        <v>0.6514815378189085</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -710,13 +710,13 @@
         <v>2020</v>
       </c>
       <c r="C12" t="n">
-        <v>2.61</v>
+        <v>3.050000000000001</v>
       </c>
       <c r="D12" t="n">
-        <v>1.570830345153809</v>
+        <v>2.0580735206604</v>
       </c>
       <c r="E12" t="n">
-        <v>1.039169654846191</v>
+        <v>0.9919264793396003</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -734,13 +734,13 @@
         <v>2021</v>
       </c>
       <c r="C13" t="n">
-        <v>2.28</v>
+        <v>4.39</v>
       </c>
       <c r="D13" t="n">
-        <v>3.578847169876099</v>
+        <v>2.299805641174316</v>
       </c>
       <c r="E13" t="n">
-        <v>1.298847169876099</v>
+        <v>2.090194358825683</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -758,13 +758,13 @@
         <v>2022</v>
       </c>
       <c r="C14" t="n">
-        <v>3.050000000000001</v>
+        <v>5.700000000000001</v>
       </c>
       <c r="D14" t="n">
-        <v>7.087985515594482</v>
+        <v>1.458372354507446</v>
       </c>
       <c r="E14" t="n">
-        <v>4.037985515594482</v>
+        <v>4.241627645492555</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -782,13 +782,13 @@
         <v>2023</v>
       </c>
       <c r="C15" t="n">
-        <v>4.39</v>
+        <v>8.159999999999998</v>
       </c>
       <c r="D15" t="n">
-        <v>11.80896949768066</v>
+        <v>0.6593026518821716</v>
       </c>
       <c r="E15" t="n">
-        <v>7.418969497680664</v>
+        <v>7.500697348117827</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -806,13 +806,13 @@
         <v>2024</v>
       </c>
       <c r="C16" t="n">
-        <v>5.700000000000001</v>
+        <v>14.4</v>
       </c>
       <c r="D16" t="n">
-        <v>12.85237693786621</v>
+        <v>1.377218961715698</v>
       </c>
       <c r="E16" t="n">
-        <v>7.15237693786621</v>
+        <v>13.0227810382843</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -830,13 +830,13 @@
         <v>2020</v>
       </c>
       <c r="C17" t="n">
-        <v>8.159999999999998</v>
+        <v>21.71</v>
       </c>
       <c r="D17" t="n">
-        <v>1.475672364234924</v>
+        <v>2.042850255966187</v>
       </c>
       <c r="E17" t="n">
-        <v>6.684327635765074</v>
+        <v>19.66714974403381</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -854,13 +854,13 @@
         <v>2021</v>
       </c>
       <c r="C18" t="n">
-        <v>14.4</v>
+        <v>37.23999999999999</v>
       </c>
       <c r="D18" t="n">
-        <v>4.027976036071777</v>
+        <v>2.538030624389648</v>
       </c>
       <c r="E18" t="n">
-        <v>10.37202396392822</v>
+        <v>34.70196937561035</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -878,13 +878,13 @@
         <v>2022</v>
       </c>
       <c r="C19" t="n">
-        <v>21.71</v>
+        <v>52.72000000000001</v>
       </c>
       <c r="D19" t="n">
-        <v>9.362483024597168</v>
+        <v>0.9455181956291199</v>
       </c>
       <c r="E19" t="n">
-        <v>12.34751697540283</v>
+        <v>51.77448180437089</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -902,13 +902,13 @@
         <v>2023</v>
       </c>
       <c r="C20" t="n">
-        <v>37.23999999999999</v>
+        <v>5.4</v>
       </c>
       <c r="D20" t="n">
-        <v>10.82515335083008</v>
+        <v>0.7079025506973267</v>
       </c>
       <c r="E20" t="n">
-        <v>26.41484664916992</v>
+        <v>4.692097449302674</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -926,13 +926,13 @@
         <v>2024</v>
       </c>
       <c r="C21" t="n">
-        <v>52.72000000000001</v>
+        <v>11.31</v>
       </c>
       <c r="D21" t="n">
-        <v>13.32500076293945</v>
+        <v>1.305465817451477</v>
       </c>
       <c r="E21" t="n">
-        <v>39.39499923706056</v>
+        <v>10.00453418254852</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -950,13 +950,13 @@
         <v>2020</v>
       </c>
       <c r="C22" t="n">
-        <v>5.4</v>
+        <v>18.79</v>
       </c>
       <c r="D22" t="n">
-        <v>1.318474292755127</v>
+        <v>1.983259439468384</v>
       </c>
       <c r="E22" t="n">
-        <v>4.081525707244873</v>
+        <v>16.80674056053162</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -974,13 +974,13 @@
         <v>2021</v>
       </c>
       <c r="C23" t="n">
-        <v>11.31</v>
+        <v>34.91</v>
       </c>
       <c r="D23" t="n">
-        <v>3.977211475372314</v>
+        <v>2.686444997787476</v>
       </c>
       <c r="E23" t="n">
-        <v>7.332788524627686</v>
+        <v>32.22355500221253</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -998,13 +998,13 @@
         <v>2022</v>
       </c>
       <c r="C24" t="n">
-        <v>18.79</v>
+        <v>30.53</v>
       </c>
       <c r="D24" t="n">
-        <v>8.891157150268555</v>
+        <v>1.313211560249329</v>
       </c>
       <c r="E24" t="n">
-        <v>9.898842849731444</v>
+        <v>29.21678843975067</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1022,13 +1022,13 @@
         <v>2023</v>
       </c>
       <c r="C25" t="n">
-        <v>34.91</v>
+        <v>7.719999999999998</v>
       </c>
       <c r="D25" t="n">
-        <v>11.33344841003418</v>
+        <v>0.5640384554862976</v>
       </c>
       <c r="E25" t="n">
-        <v>23.57655158996582</v>
+        <v>7.1559615445137</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1046,13 +1046,13 @@
         <v>2024</v>
       </c>
       <c r="C26" t="n">
-        <v>30.53</v>
+        <v>10.77</v>
       </c>
       <c r="D26" t="n">
-        <v>11.01781272888184</v>
+        <v>1.334681153297424</v>
       </c>
       <c r="E26" t="n">
-        <v>19.51218727111817</v>
+        <v>9.435318846702572</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1070,13 +1070,13 @@
         <v>2020</v>
       </c>
       <c r="C27" t="n">
-        <v>7.719999999999998</v>
+        <v>14.27</v>
       </c>
       <c r="D27" t="n">
-        <v>1.154457569122314</v>
+        <v>2.019418478012085</v>
       </c>
       <c r="E27" t="n">
-        <v>6.565542430877684</v>
+        <v>12.25058152198792</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1094,13 +1094,13 @@
         <v>2021</v>
       </c>
       <c r="C28" t="n">
-        <v>10.77</v>
+        <v>17.73</v>
       </c>
       <c r="D28" t="n">
-        <v>4.515361309051514</v>
+        <v>1.871747136116028</v>
       </c>
       <c r="E28" t="n">
-        <v>6.254638690948482</v>
+        <v>15.85825286388398</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1118,13 +1118,13 @@
         <v>2022</v>
       </c>
       <c r="C29" t="n">
-        <v>14.27</v>
+        <v>17.92</v>
       </c>
       <c r="D29" t="n">
-        <v>8.234848976135254</v>
+        <v>1.192248940467834</v>
       </c>
       <c r="E29" t="n">
-        <v>6.035151023864747</v>
+        <v>16.72775105953216</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1142,13 +1142,13 @@
         <v>2023</v>
       </c>
       <c r="C30" t="n">
-        <v>17.73</v>
+        <v>7.56</v>
       </c>
       <c r="D30" t="n">
-        <v>11.89977550506592</v>
+        <v>0.7446480989456177</v>
       </c>
       <c r="E30" t="n">
-        <v>5.830224494934086</v>
+        <v>6.815351901054382</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1166,13 +1166,13 @@
         <v>2024</v>
       </c>
       <c r="C31" t="n">
-        <v>17.92</v>
+        <v>14.4</v>
       </c>
       <c r="D31" t="n">
-        <v>14.78018760681152</v>
+        <v>1.314406514167786</v>
       </c>
       <c r="E31" t="n">
-        <v>3.139812393188475</v>
+        <v>13.08559348583221</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1190,13 +1190,13 @@
         <v>2020</v>
       </c>
       <c r="C32" t="n">
-        <v>7.56</v>
+        <v>18.51</v>
       </c>
       <c r="D32" t="n">
-        <v>1.703725576400757</v>
+        <v>2.198357343673706</v>
       </c>
       <c r="E32" t="n">
-        <v>5.856274423599243</v>
+        <v>16.3116426563263</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1214,13 +1214,13 @@
         <v>2021</v>
       </c>
       <c r="C33" t="n">
-        <v>14.4</v>
+        <v>19.28000000000001</v>
       </c>
       <c r="D33" t="n">
-        <v>3.819394111633301</v>
+        <v>1.836678624153137</v>
       </c>
       <c r="E33" t="n">
-        <v>10.5806058883667</v>
+        <v>17.44332137584687</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1238,13 +1238,13 @@
         <v>2022</v>
       </c>
       <c r="C34" t="n">
-        <v>18.51</v>
+        <v>14.47</v>
       </c>
       <c r="D34" t="n">
-        <v>7.622506618499756</v>
+        <v>1.20812714099884</v>
       </c>
       <c r="E34" t="n">
-        <v>10.88749338150025</v>
+        <v>13.26187285900116</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1262,13 +1262,13 @@
         <v>2023</v>
       </c>
       <c r="C35" t="n">
-        <v>19.28000000000001</v>
+        <v>3.319999999999999</v>
       </c>
       <c r="D35" t="n">
-        <v>11.50201225280762</v>
+        <v>0.7267984747886658</v>
       </c>
       <c r="E35" t="n">
-        <v>7.777987747192391</v>
+        <v>2.593201525211334</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1286,13 +1286,13 @@
         <v>2024</v>
       </c>
       <c r="C36" t="n">
-        <v>14.47</v>
+        <v>4.539999999999998</v>
       </c>
       <c r="D36" t="n">
-        <v>13.81128311157227</v>
+        <v>1.775436162948608</v>
       </c>
       <c r="E36" t="n">
-        <v>0.658716888427735</v>
+        <v>2.76456383705139</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -1310,13 +1310,13 @@
         <v>2020</v>
       </c>
       <c r="C37" t="n">
-        <v>3.319999999999999</v>
+        <v>5.22</v>
       </c>
       <c r="D37" t="n">
-        <v>1.661835908889771</v>
+        <v>2.336858749389648</v>
       </c>
       <c r="E37" t="n">
-        <v>1.658164091110229</v>
+        <v>2.883141250610351</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -1334,13 +1334,13 @@
         <v>2021</v>
       </c>
       <c r="C38" t="n">
-        <v>4.539999999999998</v>
+        <v>6.659999999999998</v>
       </c>
       <c r="D38" t="n">
-        <v>4.257586002349854</v>
+        <v>2.050341606140137</v>
       </c>
       <c r="E38" t="n">
-        <v>0.2824139976501447</v>
+        <v>4.609658393859862</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -1358,13 +1358,13 @@
         <v>2022</v>
       </c>
       <c r="C39" t="n">
-        <v>5.22</v>
+        <v>8.039999999999997</v>
       </c>
       <c r="D39" t="n">
-        <v>7.048264503479004</v>
+        <v>1.545534014701843</v>
       </c>
       <c r="E39" t="n">
-        <v>1.828264503479004</v>
+        <v>6.494465985298154</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -1382,13 +1382,13 @@
         <v>2023</v>
       </c>
       <c r="C40" t="n">
-        <v>6.659999999999998</v>
+        <v>3.35</v>
       </c>
       <c r="D40" t="n">
-        <v>10.381178855896</v>
+        <v>0.6911394596099854</v>
       </c>
       <c r="E40" t="n">
-        <v>3.721178855895998</v>
+        <v>2.658860540390015</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -1406,13 +1406,13 @@
         <v>2024</v>
       </c>
       <c r="C41" t="n">
-        <v>8.039999999999997</v>
+        <v>5.62</v>
       </c>
       <c r="D41" t="n">
-        <v>11.93783855438232</v>
+        <v>1.116345167160034</v>
       </c>
       <c r="E41" t="n">
-        <v>3.897838554382327</v>
+        <v>4.503654832839966</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -1430,13 +1430,13 @@
         <v>2020</v>
       </c>
       <c r="C42" t="n">
-        <v>3.35</v>
+        <v>4.75</v>
       </c>
       <c r="D42" t="n">
-        <v>1.38407289981842</v>
+        <v>2.086880445480347</v>
       </c>
       <c r="E42" t="n">
-        <v>1.96592710018158</v>
+        <v>2.663119554519653</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -1454,13 +1454,13 @@
         <v>2021</v>
       </c>
       <c r="C43" t="n">
-        <v>5.62</v>
+        <v>5.23</v>
       </c>
       <c r="D43" t="n">
-        <v>3.732655763626099</v>
+        <v>2.189149141311646</v>
       </c>
       <c r="E43" t="n">
-        <v>1.887344236373901</v>
+        <v>3.040850858688355</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -1478,13 +1478,13 @@
         <v>2022</v>
       </c>
       <c r="C44" t="n">
-        <v>4.75</v>
+        <v>5.25</v>
       </c>
       <c r="D44" t="n">
-        <v>8.02225399017334</v>
+        <v>1.310522556304932</v>
       </c>
       <c r="E44" t="n">
-        <v>3.27225399017334</v>
+        <v>3.939477443695068</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -1502,13 +1502,13 @@
         <v>2023</v>
       </c>
       <c r="C45" t="n">
-        <v>5.23</v>
+        <v>21.43</v>
       </c>
       <c r="D45" t="n">
-        <v>12.92211151123047</v>
+        <v>0.61919766664505</v>
       </c>
       <c r="E45" t="n">
-        <v>7.692111511230468</v>
+        <v>20.81080233335495</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -1526,13 +1526,13 @@
         <v>2024</v>
       </c>
       <c r="C46" t="n">
-        <v>5.25</v>
+        <v>20.89</v>
       </c>
       <c r="D46" t="n">
-        <v>14.53589916229248</v>
+        <v>1.656608104705811</v>
       </c>
       <c r="E46" t="n">
-        <v>9.28589916229248</v>
+        <v>19.23339189529419</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -1550,13 +1550,13 @@
         <v>2020</v>
       </c>
       <c r="C47" t="n">
-        <v>21.43</v>
+        <v>24.32</v>
       </c>
       <c r="D47" t="n">
-        <v>2.055251598358154</v>
+        <v>1.980499029159546</v>
       </c>
       <c r="E47" t="n">
-        <v>19.37474840164185</v>
+        <v>22.33950097084045</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -1574,13 +1574,13 @@
         <v>2021</v>
       </c>
       <c r="C48" t="n">
-        <v>20.89</v>
+        <v>31.52</v>
       </c>
       <c r="D48" t="n">
-        <v>4.553450584411621</v>
+        <v>2.46196460723877</v>
       </c>
       <c r="E48" t="n">
-        <v>16.33654941558838</v>
+        <v>29.05803539276123</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -1598,13 +1598,13 @@
         <v>2022</v>
       </c>
       <c r="C49" t="n">
-        <v>24.32</v>
+        <v>35.45</v>
       </c>
       <c r="D49" t="n">
-        <v>9.793148040771484</v>
+        <v>1.034741759300232</v>
       </c>
       <c r="E49" t="n">
-        <v>14.52685195922852</v>
+        <v>34.41525824069977</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -1622,13 +1622,13 @@
         <v>2023</v>
       </c>
       <c r="C50" t="n">
-        <v>31.52</v>
+        <v>1.86</v>
       </c>
       <c r="D50" t="n">
-        <v>12.71726703643799</v>
+        <v>0.9203199744224548</v>
       </c>
       <c r="E50" t="n">
-        <v>18.80273296356201</v>
+        <v>0.939680025577545</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -1646,13 +1646,13 @@
         <v>2024</v>
       </c>
       <c r="C51" t="n">
-        <v>35.45</v>
+        <v>2.6</v>
       </c>
       <c r="D51" t="n">
-        <v>16.17083549499512</v>
+        <v>1.800827860832214</v>
       </c>
       <c r="E51" t="n">
-        <v>19.27916450500489</v>
+        <v>0.7991721391677857</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -1670,13 +1670,13 @@
         <v>2020</v>
       </c>
       <c r="C52" t="n">
-        <v>1.86</v>
+        <v>3.689999999999999</v>
       </c>
       <c r="D52" t="n">
-        <v>1.97025740146637</v>
+        <v>2.435882806777954</v>
       </c>
       <c r="E52" t="n">
-        <v>0.1102574014663698</v>
+        <v>1.254117193222045</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -1694,13 +1694,13 @@
         <v>2021</v>
       </c>
       <c r="C53" t="n">
-        <v>2.6</v>
+        <v>4.6</v>
       </c>
       <c r="D53" t="n">
-        <v>4.684609889984131</v>
+        <v>2.161921739578247</v>
       </c>
       <c r="E53" t="n">
-        <v>2.084609889984131</v>
+        <v>2.438078260421753</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -1718,13 +1718,13 @@
         <v>2022</v>
       </c>
       <c r="C54" t="n">
-        <v>3.689999999999999</v>
+        <v>4</v>
       </c>
       <c r="D54" t="n">
-        <v>7.211582660675049</v>
+        <v>1.376484870910645</v>
       </c>
       <c r="E54" t="n">
-        <v>3.52158266067505</v>
+        <v>2.623515129089355</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -1742,13 +1742,13 @@
         <v>2023</v>
       </c>
       <c r="C55" t="n">
-        <v>4.6</v>
+        <v>3.25</v>
       </c>
       <c r="D55" t="n">
-        <v>10.57202911376953</v>
+        <v>0.7270172238349915</v>
       </c>
       <c r="E55" t="n">
-        <v>5.972029113769532</v>
+        <v>2.522982776165009</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -1766,13 +1766,13 @@
         <v>2024</v>
       </c>
       <c r="C56" t="n">
-        <v>4</v>
+        <v>6.260000000000001</v>
       </c>
       <c r="D56" t="n">
-        <v>12.14685153961182</v>
+        <v>1.598899722099304</v>
       </c>
       <c r="E56" t="n">
-        <v>8.146851539611816</v>
+        <v>4.661100277900696</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -1790,13 +1790,13 @@
         <v>2020</v>
       </c>
       <c r="C57" t="n">
-        <v>3.25</v>
+        <v>9.939999999999998</v>
       </c>
       <c r="D57" t="n">
-        <v>1.474792242050171</v>
+        <v>2.053001642227173</v>
       </c>
       <c r="E57" t="n">
-        <v>1.775207757949829</v>
+        <v>7.886998357772825</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -1814,13 +1814,13 @@
         <v>2021</v>
       </c>
       <c r="C58" t="n">
-        <v>6.260000000000001</v>
+        <v>11.53</v>
       </c>
       <c r="D58" t="n">
-        <v>3.484375953674316</v>
+        <v>2.351109743118286</v>
       </c>
       <c r="E58" t="n">
-        <v>2.775624046325684</v>
+        <v>9.178890256881719</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -1838,13 +1838,13 @@
         <v>2022</v>
       </c>
       <c r="C59" t="n">
-        <v>9.939999999999998</v>
+        <v>7.490000000000002</v>
       </c>
       <c r="D59" t="n">
-        <v>6.807424068450928</v>
+        <v>1.249347805976868</v>
       </c>
       <c r="E59" t="n">
-        <v>3.13257593154907</v>
+        <v>6.240652194023134</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -1862,13 +1862,13 @@
         <v>2023</v>
       </c>
       <c r="C60" t="n">
-        <v>11.53</v>
+        <v>3.14</v>
       </c>
       <c r="D60" t="n">
-        <v>9.160512924194336</v>
+        <v>1.128198146820068</v>
       </c>
       <c r="E60" t="n">
-        <v>2.369487075805669</v>
+        <v>2.011801853179931</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -1886,13 +1886,13 @@
         <v>2024</v>
       </c>
       <c r="C61" t="n">
-        <v>7.490000000000002</v>
+        <v>3.819999999999999</v>
       </c>
       <c r="D61" t="n">
-        <v>15.63239192962646</v>
+        <v>0.7959875464439392</v>
       </c>
       <c r="E61" t="n">
-        <v>8.142391929626463</v>
+        <v>3.02401245355606</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -1910,13 +1910,13 @@
         <v>2020</v>
       </c>
       <c r="C62" t="n">
-        <v>3.14</v>
+        <v>4.86</v>
       </c>
       <c r="D62" t="n">
-        <v>1.198125958442688</v>
+        <v>2.119656801223755</v>
       </c>
       <c r="E62" t="n">
-        <v>1.941874041557312</v>
+        <v>2.740343198776245</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -1934,13 +1934,13 @@
         <v>2021</v>
       </c>
       <c r="C63" t="n">
-        <v>3.819999999999999</v>
+        <v>6.779999999999998</v>
       </c>
       <c r="D63" t="n">
-        <v>4.532856941223145</v>
+        <v>2.473949193954468</v>
       </c>
       <c r="E63" t="n">
-        <v>0.7128569412231451</v>
+        <v>4.306050806045531</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -1958,13 +1958,13 @@
         <v>2022</v>
       </c>
       <c r="C64" t="n">
-        <v>4.86</v>
+        <v>6.789999999999999</v>
       </c>
       <c r="D64" t="n">
-        <v>9.533661842346191</v>
+        <v>1.176938533782959</v>
       </c>
       <c r="E64" t="n">
-        <v>4.673661842346191</v>
+        <v>5.61306146621704</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -1982,13 +1982,13 @@
         <v>2023</v>
       </c>
       <c r="C65" t="n">
-        <v>6.779999999999998</v>
+        <v>10.55</v>
       </c>
       <c r="D65" t="n">
-        <v>13.85664081573486</v>
+        <v>0.9410402178764343</v>
       </c>
       <c r="E65" t="n">
-        <v>7.076640815734865</v>
+        <v>9.608959782123568</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -2006,13 +2006,13 @@
         <v>2024</v>
       </c>
       <c r="C66" t="n">
-        <v>6.789999999999999</v>
+        <v>20.09</v>
       </c>
       <c r="D66" t="n">
-        <v>16.89642333984375</v>
+        <v>1.225855469703674</v>
       </c>
       <c r="E66" t="n">
-        <v>10.10642333984375</v>
+        <v>18.86414453029633</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -2030,13 +2030,13 @@
         <v>2020</v>
       </c>
       <c r="C67" t="n">
-        <v>10.55</v>
+        <v>33.84000000000001</v>
       </c>
       <c r="D67" t="n">
-        <v>1.613915801048279</v>
+        <v>2.144594430923462</v>
       </c>
       <c r="E67" t="n">
-        <v>8.936084198951724</v>
+        <v>31.69540556907655</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -2054,13 +2054,13 @@
         <v>2021</v>
       </c>
       <c r="C68" t="n">
-        <v>20.09</v>
+        <v>39.42</v>
       </c>
       <c r="D68" t="n">
-        <v>3.919536113739014</v>
+        <v>2.287207365036011</v>
       </c>
       <c r="E68" t="n">
-        <v>16.17046388626099</v>
+        <v>37.13279263496399</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -2078,13 +2078,13 @@
         <v>2022</v>
       </c>
       <c r="C69" t="n">
-        <v>33.84000000000001</v>
+        <v>35.99000000000002</v>
       </c>
       <c r="D69" t="n">
-        <v>9.089262008666992</v>
+        <v>1.329734325408936</v>
       </c>
       <c r="E69" t="n">
-        <v>24.75073799133302</v>
+        <v>34.66026567459108</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -2102,13 +2102,13 @@
         <v>2023</v>
       </c>
       <c r="C70" t="n">
-        <v>39.42</v>
+        <v>4.56</v>
       </c>
       <c r="D70" t="n">
-        <v>11.88832092285156</v>
+        <v>1.752129912376404</v>
       </c>
       <c r="E70" t="n">
-        <v>27.53167907714844</v>
+        <v>2.807870087623597</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -2126,13 +2126,13 @@
         <v>2024</v>
       </c>
       <c r="C71" t="n">
-        <v>35.99000000000002</v>
+        <v>5.9</v>
       </c>
       <c r="D71" t="n">
-        <v>12.95241641998291</v>
+        <v>2.295895338058472</v>
       </c>
       <c r="E71" t="n">
-        <v>23.03758358001711</v>
+        <v>3.604104661941529</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
